--- a/Perf/vm-small/spec2006.xlsx
+++ b/Perf/vm-small/spec2006.xlsx
@@ -673,7 +673,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -708,6 +708,9 @@
         <v>470</v>
       </c>
       <c r="L1" s="1" t="n">
+        <v>481</v>
+      </c>
+      <c r="M1" s="1" t="n">
         <v>482</v>
       </c>
     </row>
@@ -748,6 +751,9 @@
         <v>6508613915</v>
       </c>
       <c r="L2" t="n">
+        <v>448465688</v>
+      </c>
+      <c r="M2" t="n">
         <v>6985504683</v>
       </c>
     </row>
@@ -788,6 +794,9 @@
         <v>2314073808</v>
       </c>
       <c r="L3" t="n">
+        <v>167313224</v>
+      </c>
+      <c r="M3" t="n">
         <v>2758941068</v>
       </c>
     </row>
@@ -828,6 +837,9 @@
         <v>47828004</v>
       </c>
       <c r="L4" t="n">
+        <v>590516</v>
+      </c>
+      <c r="M4" t="n">
         <v>25666248</v>
       </c>
     </row>
@@ -868,6 +880,9 @@
         <v>516455807</v>
       </c>
       <c r="L5" t="n">
+        <v>4499957</v>
+      </c>
+      <c r="M5" t="n">
         <v>119207970</v>
       </c>
     </row>
@@ -908,6 +923,9 @@
         <v>144061</v>
       </c>
       <c r="L6" t="n">
+        <v>258040</v>
+      </c>
+      <c r="M6" t="n">
         <v>5034723</v>
       </c>
     </row>
@@ -948,6 +966,9 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
         <v>0</v>
       </c>
     </row>
